--- a/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>TRON</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -730,8 +731,11 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,8 +781,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +903,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,8 +1001,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -995,11 +1015,11 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1007,12 +1027,12 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,43 +1120,44 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
@@ -1141,8 +1168,11 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1150,34 +1180,34 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1188,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1240,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1216,34 +1250,34 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1254,8 +1288,11 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,8 +1338,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,43 +1388,46 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1100</v>
       </c>
       <c r="K23" s="3">
         <v>1100</v>
       </c>
       <c r="L23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1438,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,43 +1538,46 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1100</v>
       </c>
       <c r="K26" s="3">
         <v>1100</v>
       </c>
       <c r="L26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1536,43 +1588,46 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1100</v>
       </c>
       <c r="K27" s="3">
         <v>1100</v>
       </c>
       <c r="L27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1583,8 +1638,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1838,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1780,34 +1850,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1818,43 +1888,46 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1100</v>
       </c>
       <c r="K33" s="3">
         <v>1100</v>
       </c>
       <c r="L33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1865,8 +1938,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,43 +1988,46 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1100</v>
       </c>
       <c r="K35" s="3">
         <v>1100</v>
       </c>
       <c r="L35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -1959,49 +2038,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2011,8 +2093,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,8 +2135,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2058,35 +2145,35 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2233,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2190,8 +2283,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,41 +2333,44 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>600</v>
       </c>
       <c r="J45" s="3">
         <v>600</v>
       </c>
       <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,44 +2383,47 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,28 +2433,31 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E47" s="3">
         <v>20300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>76100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>75500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>74400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>185000</v>
       </c>
       <c r="J47" s="3">
         <v>185000</v>
@@ -2363,8 +2468,8 @@
       <c r="L47" s="3">
         <v>185000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>185000</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2378,8 +2483,11 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2425,8 +2533,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,8 +2683,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2577,8 +2697,8 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2587,23 +2707,23 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,44 +2783,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E54" s="3">
         <v>20600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>76500</v>
       </c>
       <c r="G54" s="3">
         <v>76500</v>
       </c>
       <c r="H54" s="3">
+        <v>76500</v>
+      </c>
+      <c r="I54" s="3">
         <v>75700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>186700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>187100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>187700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>188300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,8 +2875,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2777,8 +2908,8 @@
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2792,8 +2923,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2818,17 +2952,17 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>100</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>100</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -2839,43 +2973,46 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -2886,44 +3023,47 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
-      </c>
-      <c r="K60" s="3">
-        <v>300</v>
       </c>
       <c r="L60" s="3">
         <v>300</v>
       </c>
       <c r="M60" s="3">
+        <v>300</v>
+      </c>
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,8 +3073,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2980,8 +3123,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2989,32 +3135,32 @@
         <v>7600</v>
       </c>
       <c r="E62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F62" s="3">
         <v>7400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,8 +3323,11 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3177,35 +3335,35 @@
         <v>11600</v>
       </c>
       <c r="E66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F66" s="3">
         <v>10500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,43 +3593,46 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-500</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,43 +3793,46 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E76" s="3">
         <v>9000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>67100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>67900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>177700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>169500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168300</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,49 +3893,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3756,43 +3948,46 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1100</v>
       </c>
       <c r="K81" s="3">
         <v>1100</v>
       </c>
       <c r="L81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3803,8 +3998,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4020,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3869,8 +4068,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,43 +4318,46 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4151,8 +4368,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,8 +4390,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,8 +4538,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4320,34 +4550,34 @@
         <v>-200</v>
       </c>
       <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>56500</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4358,8 +4588,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,8 +4808,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4574,35 +4820,35 @@
         <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-56500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-110800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>188200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4612,8 +4858,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4659,44 +4908,47 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-200</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
       </c>
       <c r="I102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,6 +4956,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>TRON</t>
   </si>
@@ -656,86 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +791,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +847,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +929,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1037,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1018,27 +1057,27 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1093,14 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,49 +1172,51 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
         <v>200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>200</v>
+      </c>
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1200</v>
       </c>
       <c r="J17" s="3">
         <v>600</v>
       </c>
       <c r="K17" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="L17" s="3">
         <v>600</v>
       </c>
       <c r="M17" s="3">
+        <v>500</v>
+      </c>
+      <c r="N17" s="3">
+        <v>600</v>
+      </c>
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1171,8 +1224,14 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,40 +1239,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
       </c>
       <c r="J18" s="3">
         <v>-600</v>
       </c>
       <c r="K18" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="L18" s="3">
         <v>-600</v>
       </c>
       <c r="M18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1221,8 +1280,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,40 +1317,40 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>7800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1291,8 +1358,14 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1341,8 +1414,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,49 +1470,55 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>900</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>7300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1441,8 +1526,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1582,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,49 +1638,55 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>900</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1591,49 +1694,55 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1641,8 +1750,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1850,40 +1989,40 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-7800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1891,49 +2030,55 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>900</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -1941,8 +2086,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,49 +2142,55 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>900</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2041,63 +2198,75 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,8 +2307,10 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2148,46 +2321,52 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,8 +2415,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2286,8 +2471,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,8 +2527,14 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2345,38 +2542,38 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>300</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,84 +2583,96 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3">
         <v>200</v>
       </c>
       <c r="G46" s="3">
+        <v>300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>200</v>
+      </c>
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F47" s="3">
         <v>20700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>20300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>19800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>76100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>75500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>74400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>185000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>185000</v>
       </c>
       <c r="L47" s="3">
         <v>185000</v>
@@ -2471,11 +2680,11 @@
       <c r="M47" s="3">
         <v>185000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>185000</v>
+      </c>
+      <c r="O47" s="3">
+        <v>185000</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2486,8 +2695,14 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2536,8 +2751,14 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2807,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,19 +2919,25 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2710,34 +2949,40 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +3031,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F54" s="3">
         <v>20900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>76500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>76500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>75700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>186700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>187100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>187700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>188300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,8 +3135,10 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2911,11 +3172,11 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -2926,8 +3187,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2955,70 +3222,76 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F59" s="3">
         <v>4000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3026,58 +3299,70 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3126,47 +3411,53 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>7400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>16300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>17900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>19600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3467,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3635,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F66" s="3">
         <v>11600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>16700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>18300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>20000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,8 +3937,14 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3605,40 +3952,40 @@
         <v>-11400</v>
       </c>
       <c r="E72" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="G72" s="3">
         <v>-11300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-9000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-7600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-7900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-7300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-15500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-500</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3646,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,49 +4161,55 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F76" s="3">
         <v>9300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>67100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>67900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>66500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>177700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>170400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>169500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>168300</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -3846,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,104 +4273,116 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>900</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4001,8 +4390,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4416,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4071,8 +4468,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,8 +4748,14 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4330,40 +4763,40 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-500</v>
       </c>
       <c r="L89" s="3">
         <v>-300</v>
       </c>
       <c r="M89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4371,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4830,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,49 +4994,55 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>16200</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3">
         <v>56500</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,58 +5296,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>200</v>
+        <v>-16200</v>
       </c>
       <c r="E100" s="3">
         <v>200</v>
       </c>
       <c r="F100" s="3">
+        <v>200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>200</v>
+      </c>
+      <c r="H100" s="3">
         <v>-56500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-110800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>188200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4911,8 +5408,14 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4920,45 +5423,51 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRON_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>TRON</t>
   </si>
@@ -656,129 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E8" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="3">
         <v>1100</v>
       </c>
       <c r="G8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E9" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="F9" s="3">
         <v>800</v>
       </c>
       <c r="G9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>800</v>
+      </c>
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -792,13 +811,13 @@
         <v>300</v>
       </c>
       <c r="G10" s="3">
+        <v>300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
         <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>300</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
@@ -809,8 +828,14 @@
       <c r="L10" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3">
+        <v>300</v>
+      </c>
+      <c r="N10" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +848,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +882,14 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,23 +920,29 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-14000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-2200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -919,13 +958,19 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -934,13 +979,13 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -951,8 +996,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +1013,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2700</v>
       </c>
       <c r="K17" s="3">
         <v>2000</v>
       </c>
       <c r="L17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,31 +1105,33 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2100</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
@@ -1072,40 +1139,52 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1124,64 +1203,76 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="F23" s="3">
         <v>15600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1200,8 +1291,14 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1329,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F26" s="3">
         <v>12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F27" s="3">
         <v>12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1443,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1481,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1519,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,31 +1557,37 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F32" s="3">
         <v>2100</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
@@ -1456,40 +1595,52 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F33" s="3">
         <v>12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1671,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F35" s="3">
         <v>12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1772,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,57 +1788,65 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F41" s="3">
         <v>10600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1681,40 +1860,52 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>800</v>
       </c>
       <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>800</v>
+      </c>
+      <c r="M43" s="3">
+        <v>700</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1725,104 +1916,122 @@
         <v>700</v>
       </c>
       <c r="F44" s="3">
+        <v>700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>700</v>
+      </c>
+      <c r="H44" s="3">
         <v>1000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F46" s="3">
         <v>12800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4500</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>200</v>
+      </c>
+      <c r="F47" s="3">
         <v>228400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -1841,72 +2050,90 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
       <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>2600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2164,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,23 +2202,29 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>225100</v>
       </c>
       <c r="E52" s="3">
+        <v>198100</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>102200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2001,8 +2240,14 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2278,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>211400</v>
+      </c>
+      <c r="F54" s="3">
         <v>244600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>112200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2336,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,40 +2352,48 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2134,20 +2401,20 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2157,8 +2424,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2174,66 +2447,78 @@
       <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F60" s="3">
         <v>800</v>
       </c>
       <c r="G60" s="3">
+        <v>800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>800</v>
+      </c>
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2253,8 +2538,14 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2285,8 +2576,14 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2614,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2652,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2690,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F66" s="3">
         <v>4800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2748,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2782,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2820,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2858,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2896,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="F72" s="3">
         <v>7300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-4900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-5700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2972,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3010,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +3048,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>249900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>210300</v>
+      </c>
+      <c r="F76" s="3">
         <v>239800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>111400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3124,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F81" s="3">
         <v>12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,16 +3225,18 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -2862,8 +3259,14 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3297,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3335,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3373,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3411,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3449,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-200</v>
-      </c>
       <c r="G89" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
         <v>-200</v>
       </c>
       <c r="I89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3507,48 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3579,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3617,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+      <c r="E94" s="3">
+        <v>-100</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3675,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3709,14 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3747,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3785,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3823,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>6200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3899,48 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1200</v>
       </c>
       <c r="K102" s="3">
         <v>-400</v>
       </c>
       <c r="L102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N102" s="3">
         <v>2600</v>
       </c>
     </row>
